--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2020_la_araucania.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2020_la_araucania.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:34</t>
+    <t xml:space="preserve">2026-09-09 20:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2020_la_araucania.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2020_la_araucania.xlsx
@@ -24,45 +24,81 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Temuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cunco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curarrehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galvarino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorbea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lautaro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loncoche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipeuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nueva Imperial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padre Las Casas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perquenco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pitrufquén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pucón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saavedra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teodoro Schmidt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toltén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vilcún</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villarrica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cholchol</t>
+  </si>
+  <si>
     <t xml:space="preserve">Angol</t>
   </si>
   <si>
-    <t xml:space="preserve">Carahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cholchol</t>
-  </si>
-  <si>
     <t xml:space="preserve">Collipulli</t>
   </si>
   <si>
-    <t xml:space="preserve">Cunco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curacautín</t>
   </si>
   <si>
-    <t xml:space="preserve">Curarrehue</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ercilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Freire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galvarino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorbea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lautaro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loncoche</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lonquimay</t>
   </si>
   <si>
@@ -72,54 +108,18 @@
     <t xml:space="preserve">Lumaco</t>
   </si>
   <si>
-    <t xml:space="preserve">Melipeuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nueva Imperial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Padre Las Casas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perquenco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pitrufquén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pucón</t>
-  </si>
-  <si>
     <t xml:space="preserve">Purén</t>
   </si>
   <si>
     <t xml:space="preserve">Renaico</t>
   </si>
   <si>
-    <t xml:space="preserve">Saavedra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teodoro Schmidt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toltén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Traiguén</t>
   </si>
   <si>
     <t xml:space="preserve">Victoria</t>
   </si>
   <si>
-    <t xml:space="preserve">Vilcún</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villarrica</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:35</t>
+    <t xml:space="preserve">2026-09-18 10:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -541,7 +541,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.38</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4.22</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="5">
@@ -565,7 +565,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2.72</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.72</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="8">
@@ -589,7 +589,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="9">
@@ -597,7 +597,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -605,7 +605,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="11">
@@ -613,7 +613,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3.44</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="12">
@@ -621,7 +621,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>3.55</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="13">
@@ -629,7 +629,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2.5</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="14">
@@ -637,7 +637,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3.8</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="15">
@@ -645,7 +645,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="16">
@@ -653,7 +653,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3.79</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="17">
@@ -661,7 +661,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>5.31</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="18">
@@ -669,7 +669,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="19">
@@ -677,7 +677,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>3.23</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="20">
@@ -685,7 +685,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>3.51</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="21">
@@ -693,7 +693,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>4.77</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="22">
@@ -701,7 +701,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>3.1</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="23">
@@ -709,7 +709,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="24">
@@ -717,7 +717,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>4.71</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="25">
@@ -725,7 +725,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>3.77</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="26">
@@ -733,7 +733,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2.72</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="27">
@@ -741,7 +741,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="28">
@@ -749,7 +749,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>2.55</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="29">
@@ -757,7 +757,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>2.62</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="30">
@@ -765,7 +765,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>4.58</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="31">
@@ -773,7 +773,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>3.88</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="32">
@@ -781,7 +781,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>3.34</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="33">
@@ -789,7 +789,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>2.08</v>
+        <v>3.88</v>
       </c>
     </row>
   </sheetData>
